--- a/data/trans_camb/P16A07-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A07-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,16</t>
+          <t>-0,71; 3,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,28</t>
+          <t>-1,66; 2,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,25</t>
+          <t>0,45; 5,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,85</t>
+          <t>1,99; 6,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,37</t>
+          <t>-1,04; 4,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,83</t>
+          <t>0,8; 5,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,9</t>
+          <t>1,55; 4,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,89</t>
+          <t>-0,76; 2,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,01</t>
+          <t>1,48; 4,95</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 100,41</t>
+          <t>-16,19; 101,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 68,91</t>
+          <t>-34,16; 68,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 173,76</t>
+          <t>9,47; 164,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,77; 80,36</t>
+          <t>17,51; 78,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 49,86</t>
+          <t>-10,29; 47,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 66,18</t>
+          <t>7,37; 67,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,95; 73,52</t>
+          <t>19,72; 77,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 44,05</t>
+          <t>-9,95; 40,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,7; 76,99</t>
+          <t>18,03; 74,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,23</t>
+          <t>0,56; 2,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,64</t>
+          <t>0,12; 1,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,69</t>
+          <t>0,69; 2,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,6</t>
+          <t>-0,47; 2,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,36</t>
+          <t>0,13; 3,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 3,27</t>
+          <t>-0,26; 3,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,98</t>
+          <t>0,34; 2,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,12</t>
+          <t>0,42; 2,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,59</t>
+          <t>0,65; 2,7</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,43; 309,24</t>
+          <t>37,33; 325,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 229,68</t>
+          <t>5,14; 235,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,91; 346,54</t>
+          <t>50,49; 366,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 66,81</t>
+          <t>-9,67; 67,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 90,27</t>
+          <t>2,05; 86,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 87,46</t>
+          <t>-1,8; 83,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,61; 84,42</t>
+          <t>11,25; 91,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,39; 91,1</t>
+          <t>13,75; 90,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,03; 109,24</t>
+          <t>20,07; 115,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,93</t>
+          <t>-1,89; 1,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; -0,24</t>
+          <t>-2,95; -0,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,02</t>
+          <t>-1,61; 1,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,62</t>
+          <t>-3,67; 0,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,22</t>
+          <t>-3,06; 1,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,22</t>
+          <t>-1,95; 2,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,9</t>
+          <t>-2,2; 0,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,11</t>
+          <t>-2,56; -0,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,55</t>
+          <t>-1,01; 1,63</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,89; 159,85</t>
+          <t>-74,53; 152,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 6,22</t>
+          <t>-94,01; -2,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,41; 161,64</t>
+          <t>-59,41; 129,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-75,47; 36,66</t>
+          <t>-75,93; 38,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,67; 55,66</t>
+          <t>-65,21; 64,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 97,37</t>
+          <t>-39,98; 113,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-64,07; 51,67</t>
+          <t>-63,06; 30,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,51; 10,31</t>
+          <t>-71,87; 2,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 81,23</t>
+          <t>-30,76; 84,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,75</t>
+          <t>0,15; 1,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,76</t>
+          <t>-0,66; 0,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,92</t>
+          <t>0,2; 1,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,13</t>
+          <t>0,68; 3,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,8</t>
+          <t>-0,61; 1,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,03</t>
+          <t>-0,75; 1,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,3</t>
+          <t>0,7; 2,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,09</t>
+          <t>-0,33; 1,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,63</t>
+          <t>0,01; 1,57</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,07; 96,77</t>
+          <t>5,06; 102,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 41,78</t>
+          <t>-26,46; 40,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 107,07</t>
+          <t>8,28; 109,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,75; 52,72</t>
+          <t>9,95; 54,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 30,92</t>
+          <t>-8,61; 31,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 33,82</t>
+          <t>-10,86; 34,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,4; 57,35</t>
+          <t>15,56; 55,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 27,8</t>
+          <t>-7,39; 27,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 39,71</t>
+          <t>0,4; 40,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A07-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A07-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>2,27</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>3,36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>3,06</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,15</t>
+          <t>-0,66; 3,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,11</t>
+          <t>-1,62; 2,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,31</t>
+          <t>0,1; 4,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,91</t>
+          <t>2,08; 7,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 4,31</t>
+          <t>-1,21; 3,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,99</t>
+          <t>1,0; 5,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,98</t>
+          <t>1,42; 5,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,68</t>
+          <t>-0,72; 2,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,95</t>
+          <t>1,34; 4,81</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 101,89</t>
+          <t>-14,87; 106,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 68,01</t>
+          <t>-34,71; 64,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,47; 164,69</t>
+          <t>1,12; 145,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,51; 78,24</t>
+          <t>19,08; 80,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 47,57</t>
+          <t>-11,3; 44,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 67,67</t>
+          <t>8,68; 65,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,72; 77,3</t>
+          <t>17,71; 77,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 40,06</t>
+          <t>-8,79; 42,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,03; 74,93</t>
+          <t>16,5; 75,06</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>2,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,36</t>
+          <t>0,54; 2,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,61</t>
+          <t>0,07; 1,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,64</t>
+          <t>1,26; 3,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,61</t>
+          <t>-0,64; 2,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,27</t>
+          <t>0,21; 3,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,27</t>
+          <t>1,06; 3,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,11</t>
+          <t>0,25; 1,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,09</t>
+          <t>0,46; 2,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,7</t>
+          <t>1,41; 3,07</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163,6%</t>
+          <t>204,48%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>84,12%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,33; 325,84</t>
+          <t>35,71; 337,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 235,59</t>
+          <t>2,65; 227,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,49; 366,41</t>
+          <t>83,76; 435,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 67,93</t>
+          <t>-11,72; 63,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 86,12</t>
+          <t>4,08; 88,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 83,68</t>
+          <t>19,17; 99,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 91,76</t>
+          <t>8,01; 84,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,75; 90,18</t>
+          <t>14,04; 89,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,07; 115,33</t>
+          <t>43,98; 137,68</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-0,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,8</t>
+          <t>-1,92; 1,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,32</t>
+          <t>-2,83; -0,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,75</t>
+          <t>-1,61; 1,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 0,74</t>
+          <t>-3,65; 0,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,39</t>
+          <t>-3,44; 1,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,31</t>
+          <t>-2,16; 2,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,59</t>
+          <t>-2,32; 0,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,03</t>
+          <t>-2,45; 0,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,63</t>
+          <t>-1,17; 1,44</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>-0,0%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-74,53; 152,95</t>
+          <t>-74,27; 140,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-94,01; -2,13</t>
+          <t>-100,0; 9,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,41; 129,7</t>
+          <t>-55,38; 127,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-75,93; 38,89</t>
+          <t>-74,61; 47,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,21; 64,76</t>
+          <t>-68,29; 53,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,98; 113,28</t>
+          <t>-41,61; 92,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-63,06; 30,34</t>
+          <t>-64,25; 32,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,87; 2,94</t>
+          <t>-69,37; 5,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 84,49</t>
+          <t>-33,85; 74,36</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>1,29</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,86</t>
+          <t>0,15; 1,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,77</t>
+          <t>-0,71; 0,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,96</t>
+          <t>0,43; 2,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,2</t>
+          <t>0,55; 3,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,82</t>
+          <t>-0,71; 1,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,99</t>
+          <t>0,07; 2,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,2</t>
+          <t>0,67; 2,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,11</t>
+          <t>-0,39; 1,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,57</t>
+          <t>0,64; 1,95</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,06; 102,72</t>
+          <t>2,87; 97,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 40,91</t>
+          <t>-28,54; 42,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,28; 109,73</t>
+          <t>17,29; 116,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,95; 54,97</t>
+          <t>7,05; 53,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 31,33</t>
+          <t>-10,32; 27,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 34,18</t>
+          <t>0,98; 40,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,56; 55,77</t>
+          <t>14,67; 58,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 27,61</t>
+          <t>-8,95; 25,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 40,63</t>
+          <t>13,24; 48,58</t>
         </is>
       </c>
     </row>
